--- a/data/trans_orig/IP19D-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IP19D-Habitat-trans_orig.xlsx
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>599</t>
+          <t>584</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>5175</t>
+          <t>5061</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>6,4%</t>
+          <t>6,26%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>599</t>
+          <t>586</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>5639</t>
+          <t>5084</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>3,28%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>40472</t>
+          <t>40330</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>54107</t>
+          <t>54178</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>54,45%</t>
+          <t>54,25%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>72,79%</t>
+          <t>72,88%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>45595</t>
+          <t>45257</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>58857</t>
+          <t>58917</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>56,39%</t>
+          <t>55,97%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>72,79%</t>
+          <t>72,87%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>90672</t>
+          <t>89634</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>109689</t>
+          <t>109923</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>58,43%</t>
+          <t>57,76%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>70,68%</t>
+          <t>70,83%</t>
         </is>
       </c>
     </row>
@@ -964,7 +964,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>4802</t>
+          <t>4262</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>6,46%</t>
+          <t>5,73%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -999,7 +999,7 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>3796</t>
+          <t>3792</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>632</t>
+          <t>635</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>5561</t>
+          <t>5800</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1049,7 +1049,7 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>3,74%</t>
         </is>
       </c>
     </row>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>19075</t>
+          <t>18989</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>32294</t>
+          <t>32682</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1087,12 +1087,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>25,66%</t>
+          <t>25,54%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>43,44%</t>
+          <t>43,97%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>18853</t>
+          <t>19438</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>32248</t>
+          <t>33117</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1122,12 +1122,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>23,32%</t>
+          <t>24,04%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>39,88%</t>
+          <t>40,96%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1142,12 +1142,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>41987</t>
+          <t>41000</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>60372</t>
+          <t>61006</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>27,06%</t>
+          <t>26,42%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>38,9%</t>
+          <t>39,31%</t>
         </is>
       </c>
     </row>
@@ -1302,12 +1302,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1282</t>
+          <t>1273</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>7121</t>
+          <t>7060</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1317,12 +1317,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>6,5%</t>
+          <t>6,45%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1372,12 +1372,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1276</t>
+          <t>1269</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>7083</t>
+          <t>6464</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1392,7 +1392,7 @@
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>2,93%</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>63777</t>
+          <t>64069</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>79242</t>
+          <t>78785</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,12 +1430,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>58,23%</t>
+          <t>58,5%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>72,35%</t>
+          <t>71,93%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>55026</t>
+          <t>55398</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>72056</t>
+          <t>72432</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,12 +1465,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>49,58%</t>
+          <t>49,91%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>64,92%</t>
+          <t>65,26%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>124312</t>
+          <t>123076</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>146086</t>
+          <t>146438</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>56,37%</t>
+          <t>55,81%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>66,25%</t>
+          <t>66,41%</t>
         </is>
       </c>
     </row>
@@ -1528,12 +1528,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1058</t>
+          <t>1053</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>6631</t>
+          <t>6649</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1543,12 +1543,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>6,05%</t>
+          <t>6,07%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1563,12 +1563,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>2126</t>
+          <t>2662</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>10707</t>
+          <t>10066</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1578,12 +1578,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>9,65%</t>
+          <t>9,07%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1598,12 +1598,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>4436</t>
+          <t>5130</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>13744</t>
+          <t>14188</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1613,12 +1613,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>6,23%</t>
+          <t>6,43%</t>
         </is>
       </c>
     </row>
@@ -1641,12 +1641,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>24300</t>
+          <t>25119</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>39264</t>
+          <t>39189</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1656,12 +1656,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>22,19%</t>
+          <t>22,93%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>35,85%</t>
+          <t>35,78%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1676,12 +1676,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>33873</t>
+          <t>32895</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>50446</t>
+          <t>50078</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1691,12 +1691,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>30,52%</t>
+          <t>29,64%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>45,45%</t>
+          <t>45,12%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1711,12 +1711,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>62914</t>
+          <t>63709</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>84386</t>
+          <t>85247</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1726,12 +1726,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>28,53%</t>
+          <t>28,89%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>38,27%</t>
+          <t>38,66%</t>
         </is>
       </c>
     </row>
@@ -1911,7 +1911,7 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>4110</t>
+          <t>3598</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1926,7 +1926,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>5,33%</t>
+          <t>4,66%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1946,7 +1946,7 @@
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>3601</t>
+          <t>3593</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1984,12 +1984,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>37270</t>
+          <t>36631</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>49638</t>
+          <t>49248</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1999,12 +1999,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>54,35%</t>
+          <t>53,42%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>72,38%</t>
+          <t>71,82%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2019,12 +2019,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>43595</t>
+          <t>44250</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>56133</t>
+          <t>56892</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2034,12 +2034,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>56,51%</t>
+          <t>57,36%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>72,76%</t>
+          <t>73,74%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2054,12 +2054,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>83801</t>
+          <t>84669</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>103117</t>
+          <t>102608</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2069,12 +2069,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>57,51%</t>
+          <t>58,1%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>70,76%</t>
+          <t>70,41%</t>
         </is>
       </c>
     </row>
@@ -2097,12 +2097,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>576</t>
+          <t>630</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>5758</t>
+          <t>5815</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2112,12 +2112,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>8,4%</t>
+          <t>8,48%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2137,7 +2137,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>4183</t>
+          <t>5200</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2152,7 +2152,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>5,42%</t>
+          <t>6,74%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,12 +2167,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1358</t>
+          <t>1288</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>7871</t>
+          <t>7765</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2182,12 +2182,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>5,4%</t>
+          <t>5,33%</t>
         </is>
       </c>
     </row>
@@ -2210,12 +2210,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>16912</t>
+          <t>17219</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>29110</t>
+          <t>29491</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2225,12 +2225,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>24,66%</t>
+          <t>25,11%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>42,45%</t>
+          <t>43,01%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2245,12 +2245,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>19121</t>
+          <t>18304</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>31455</t>
+          <t>31401</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2260,12 +2260,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>24,78%</t>
+          <t>23,73%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>40,77%</t>
+          <t>40,7%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,12 +2280,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>38936</t>
+          <t>39028</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>56717</t>
+          <t>57001</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2295,12 +2295,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>26,72%</t>
+          <t>26,78%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>38,92%</t>
+          <t>39,12%</t>
         </is>
       </c>
     </row>
@@ -2445,7 +2445,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>3674</t>
+          <t>3735</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2460,7 +2460,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>4,01%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2475,12 +2475,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>646</t>
+          <t>644</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>6362</t>
+          <t>6224</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2495,7 +2495,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>7,22%</t>
+          <t>7,06%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2510,12 +2510,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>870</t>
+          <t>727</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>6885</t>
+          <t>7290</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2525,12 +2525,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>4,02%</t>
         </is>
       </c>
     </row>
@@ -2553,12 +2553,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>50686</t>
+          <t>51344</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>66858</t>
+          <t>67183</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2568,12 +2568,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>54,47%</t>
+          <t>55,18%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>71,85%</t>
+          <t>72,2%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2588,12 +2588,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>52536</t>
+          <t>53111</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>66481</t>
+          <t>67089</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2603,12 +2603,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>59,61%</t>
+          <t>60,26%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>75,43%</t>
+          <t>76,12%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2623,12 +2623,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>107849</t>
+          <t>108177</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>129389</t>
+          <t>129610</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2638,12 +2638,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>59,52%</t>
+          <t>59,71%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>71,41%</t>
+          <t>71,53%</t>
         </is>
       </c>
     </row>
@@ -2666,12 +2666,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>709</t>
+          <t>710</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>5960</t>
+          <t>5987</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2686,7 +2686,7 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>6,4%</t>
+          <t>6,43%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2701,12 +2701,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>644</t>
+          <t>649</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>5768</t>
+          <t>5582</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2716,12 +2716,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>6,54%</t>
+          <t>6,33%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2736,12 +2736,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>1934</t>
+          <t>1936</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>8401</t>
+          <t>8958</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2756,7 +2756,7 @@
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>4,64%</t>
+          <t>4,94%</t>
         </is>
       </c>
     </row>
@@ -2779,12 +2779,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>23709</t>
+          <t>23140</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>39575</t>
+          <t>38407</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2794,12 +2794,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>25,48%</t>
+          <t>24,87%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>42,53%</t>
+          <t>41,28%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2814,12 +2814,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>17640</t>
+          <t>17076</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>31657</t>
+          <t>30509</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2829,12 +2829,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>20,01%</t>
+          <t>19,37%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>35,92%</t>
+          <t>34,62%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2849,12 +2849,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>44992</t>
+          <t>44545</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>65597</t>
+          <t>65159</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2864,12 +2864,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>24,83%</t>
+          <t>24,59%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>36,2%</t>
+          <t>35,96%</t>
         </is>
       </c>
     </row>
@@ -3009,12 +3009,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>1909</t>
+          <t>1903</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>8412</t>
+          <t>7946</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3029,7 +3029,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3044,12 +3044,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>2015</t>
+          <t>1974</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>9932</t>
+          <t>9164</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3059,12 +3059,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3079,12 +3079,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>4692</t>
+          <t>4648</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>14406</t>
+          <t>14495</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,06%</t>
         </is>
       </c>
     </row>
@@ -3122,12 +3122,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>206710</t>
+          <t>207600</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>237423</t>
+          <t>237500</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3137,12 +3137,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>59,83%</t>
+          <t>60,09%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>68,72%</t>
+          <t>68,74%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3157,12 +3157,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>212105</t>
+          <t>211900</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>241785</t>
+          <t>241549</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3172,12 +3172,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>59,39%</t>
+          <t>59,33%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>67,7%</t>
+          <t>67,63%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3192,12 +3192,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>427332</t>
+          <t>427426</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>466782</t>
+          <t>469310</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3207,12 +3207,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>60,82%</t>
+          <t>60,83%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>66,43%</t>
+          <t>66,79%</t>
         </is>
       </c>
     </row>
@@ -3235,12 +3235,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>4977</t>
+          <t>5060</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>14326</t>
+          <t>14479</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3250,12 +3250,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>4,19%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3270,12 +3270,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>5328</t>
+          <t>5407</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>16165</t>
+          <t>15293</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3285,12 +3285,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>4,53%</t>
+          <t>4,28%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3305,12 +3305,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>12384</t>
+          <t>12479</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>25651</t>
+          <t>25392</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3320,12 +3320,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>3,61%</t>
         </is>
       </c>
     </row>
@@ -3348,12 +3348,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>95956</t>
+          <t>95731</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>125367</t>
+          <t>124167</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3363,12 +3363,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>27,77%</t>
+          <t>27,71%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>36,29%</t>
+          <t>35,94%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3383,12 +3383,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>101795</t>
+          <t>101640</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>130563</t>
+          <t>130696</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3398,12 +3398,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>28,5%</t>
+          <t>28,46%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>36,56%</t>
+          <t>36,6%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3418,12 +3418,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>207701</t>
+          <t>207297</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>247002</t>
+          <t>248226</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3433,12 +3433,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>29,56%</t>
+          <t>29,5%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>35,15%</t>
+          <t>35,33%</t>
         </is>
       </c>
     </row>
@@ -3815,7 +3815,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>5416</t>
+          <t>6285</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3830,7 +3830,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>7,11%</t>
+          <t>8,25%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3850,7 +3850,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>3210</t>
+          <t>3177</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3865,7 +3865,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>4,26%</t>
+          <t>4,22%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3885,7 +3885,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>7156</t>
+          <t>7382</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3900,7 +3900,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,73%</t>
+          <t>4,87%</t>
         </is>
       </c>
     </row>
@@ -3923,12 +3923,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>27541</t>
+          <t>28024</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>42371</t>
+          <t>42629</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3938,12 +3938,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>36,17%</t>
+          <t>36,8%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>55,64%</t>
+          <t>55,98%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3958,12 +3958,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>33770</t>
+          <t>33992</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>48116</t>
+          <t>48383</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3973,12 +3973,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>44,86%</t>
+          <t>45,15%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>63,92%</t>
+          <t>64,27%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3993,12 +3993,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>65430</t>
+          <t>64911</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>86629</t>
+          <t>86818</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4008,12 +4008,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>43,21%</t>
+          <t>42,87%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>57,21%</t>
+          <t>57,33%</t>
         </is>
       </c>
     </row>
@@ -4041,7 +4041,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>5457</t>
+          <t>4938</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4056,7 +4056,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>7,17%</t>
+          <t>6,48%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -4071,12 +4071,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>643</t>
+          <t>692</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>6392</t>
+          <t>6526</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4086,12 +4086,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>8,49%</t>
+          <t>8,67%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -4106,12 +4106,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1357</t>
+          <t>1369</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>8267</t>
+          <t>8221</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4126,7 +4126,7 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>5,46%</t>
+          <t>5,43%</t>
         </is>
       </c>
     </row>
@@ -4149,12 +4149,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>31047</t>
+          <t>30353</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>45221</t>
+          <t>45220</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4164,12 +4164,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>40,77%</t>
+          <t>39,86%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>59,39%</t>
+          <t>59,38%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4184,12 +4184,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>24529</t>
+          <t>23986</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>38315</t>
+          <t>38289</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4199,12 +4199,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>32,58%</t>
+          <t>31,86%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>50,9%</t>
+          <t>50,86%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4219,12 +4219,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>58239</t>
+          <t>58611</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>79952</t>
+          <t>79688</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4234,12 +4234,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>38,46%</t>
+          <t>38,71%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>52,8%</t>
+          <t>52,62%</t>
         </is>
       </c>
     </row>
@@ -4379,12 +4379,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>623</t>
+          <t>634</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>6200</t>
+          <t>5715</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -4394,12 +4394,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>5,55%</t>
+          <t>5,12%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -4414,12 +4414,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1307</t>
+          <t>1294</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>7753</t>
+          <t>8343</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -4429,12 +4429,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>6,73%</t>
+          <t>7,24%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -4449,12 +4449,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>3198</t>
+          <t>3178</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>11301</t>
+          <t>10878</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -4464,12 +4464,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>4,98%</t>
+          <t>4,79%</t>
         </is>
       </c>
     </row>
@@ -4492,12 +4492,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>52654</t>
+          <t>52241</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>68460</t>
+          <t>68346</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4507,12 +4507,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>47,13%</t>
+          <t>46,76%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>61,28%</t>
+          <t>61,17%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4527,12 +4527,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>44543</t>
+          <t>45216</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>61520</t>
+          <t>62028</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4542,12 +4542,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>38,66%</t>
+          <t>39,24%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>53,39%</t>
+          <t>53,83%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4562,12 +4562,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>101289</t>
+          <t>101663</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>126051</t>
+          <t>125164</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4577,12 +4577,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>44,63%</t>
+          <t>44,8%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>55,54%</t>
+          <t>55,15%</t>
         </is>
       </c>
     </row>
@@ -4610,7 +4610,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>4627</t>
+          <t>3914</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4625,7 +4625,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>4,14%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4640,12 +4640,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1331</t>
+          <t>1323</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>6878</t>
+          <t>7421</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4660,7 +4660,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>5,97%</t>
+          <t>6,44%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4675,12 +4675,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>2033</t>
+          <t>1977</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>9440</t>
+          <t>8585</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4690,12 +4690,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>3,78%</t>
         </is>
       </c>
     </row>
@@ -4718,12 +4718,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>39750</t>
+          <t>40329</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>55756</t>
+          <t>56180</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4733,12 +4733,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>35,58%</t>
+          <t>36,1%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>49,91%</t>
+          <t>50,29%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>46629</t>
+          <t>45854</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>63406</t>
+          <t>62586</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4768,12 +4768,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>40,47%</t>
+          <t>39,79%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>55,03%</t>
+          <t>54,32%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4788,12 +4788,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>90283</t>
+          <t>89721</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>114765</t>
+          <t>113298</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4803,12 +4803,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>39,78%</t>
+          <t>39,53%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>50,57%</t>
+          <t>49,92%</t>
         </is>
       </c>
     </row>
@@ -4953,7 +4953,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3520</t>
+          <t>3479</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4968,7 +4968,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>4,74%</t>
+          <t>4,68%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4983,12 +4983,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>424</t>
+          <t>425</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>4390</t>
+          <t>4776</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5003,7 +5003,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>5,5%</t>
+          <t>5,99%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5018,12 +5018,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>629</t>
+          <t>621</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>5694</t>
+          <t>5063</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5033,12 +5033,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>3,29%</t>
         </is>
       </c>
     </row>
@@ -5061,12 +5061,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>24456</t>
+          <t>24486</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>38056</t>
+          <t>37428</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -5076,12 +5076,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>32,9%</t>
+          <t>32,94%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>51,19%</t>
+          <t>50,35%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -5096,12 +5096,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>24620</t>
+          <t>24814</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>38725</t>
+          <t>39266</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5111,12 +5111,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>30,87%</t>
+          <t>31,11%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>48,56%</t>
+          <t>49,24%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -5131,12 +5131,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>52833</t>
+          <t>51691</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>71971</t>
+          <t>71158</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -5146,12 +5146,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>34,29%</t>
+          <t>33,55%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>46,71%</t>
+          <t>46,18%</t>
         </is>
       </c>
     </row>
@@ -5174,12 +5174,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>642</t>
+          <t>657</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>5359</t>
+          <t>5327</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5189,12 +5189,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>7,21%</t>
+          <t>7,17%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5209,12 +5209,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1635</t>
+          <t>1327</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>8860</t>
+          <t>8346</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5224,12 +5224,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>11,11%</t>
+          <t>10,47%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5244,12 +5244,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>3160</t>
+          <t>2912</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>11609</t>
+          <t>11497</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5259,12 +5259,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>7,53%</t>
+          <t>7,46%</t>
         </is>
       </c>
     </row>
@@ -5287,12 +5287,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>33678</t>
+          <t>33870</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>47087</t>
+          <t>47563</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5302,12 +5302,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>45,31%</t>
+          <t>45,56%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>63,34%</t>
+          <t>63,98%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5322,12 +5322,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>35778</t>
+          <t>35418</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>49780</t>
+          <t>49842</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5337,12 +5337,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>44,86%</t>
+          <t>44,41%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>62,42%</t>
+          <t>62,5%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5357,12 +5357,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>73336</t>
+          <t>74967</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>92576</t>
+          <t>94245</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5372,12 +5372,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>47,59%</t>
+          <t>48,65%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>60,08%</t>
+          <t>61,16%</t>
         </is>
       </c>
     </row>
@@ -5522,7 +5522,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>4027</t>
+          <t>4015</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5537,7 +5537,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>4,36%</t>
+          <t>4,35%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5557,7 +5557,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>6247</t>
+          <t>5649</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5572,7 +5572,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>6,6%</t>
+          <t>5,96%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5592,7 +5592,7 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>7067</t>
+          <t>6099</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5607,7 +5607,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>3,26%</t>
         </is>
       </c>
     </row>
@@ -5630,12 +5630,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>39092</t>
+          <t>39856</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>55902</t>
+          <t>55655</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5645,12 +5645,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>42,35%</t>
+          <t>43,18%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>60,56%</t>
+          <t>60,29%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5665,12 +5665,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>38145</t>
+          <t>38550</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>55247</t>
+          <t>55564</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5680,12 +5680,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>40,27%</t>
+          <t>40,69%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>58,32%</t>
+          <t>58,66%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5700,12 +5700,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>83052</t>
+          <t>81553</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>106870</t>
+          <t>106238</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5715,12 +5715,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>44,4%</t>
+          <t>43,6%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>57,14%</t>
+          <t>56,8%</t>
         </is>
       </c>
     </row>
@@ -5743,12 +5743,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>756</t>
+          <t>761</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>6799</t>
+          <t>6464</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -5763,7 +5763,7 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>7,37%</t>
+          <t>7,0%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -5778,12 +5778,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>2855</t>
+          <t>2325</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>10657</t>
+          <t>11116</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -5793,12 +5793,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>11,25%</t>
+          <t>11,73%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -5813,12 +5813,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>5049</t>
+          <t>5125</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>14353</t>
+          <t>14915</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -5828,12 +5828,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,74%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>7,67%</t>
+          <t>7,97%</t>
         </is>
       </c>
     </row>
@@ -5856,12 +5856,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>32420</t>
+          <t>32263</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>49336</t>
+          <t>49069</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5871,12 +5871,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>35,12%</t>
+          <t>34,95%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>53,45%</t>
+          <t>53,16%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5891,12 +5891,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>33779</t>
+          <t>32970</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>51237</t>
+          <t>49818</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5906,12 +5906,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>35,66%</t>
+          <t>34,8%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>54,09%</t>
+          <t>52,59%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5926,12 +5926,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>69956</t>
+          <t>70799</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>94080</t>
+          <t>94608</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5941,12 +5941,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>37,4%</t>
+          <t>37,85%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>50,3%</t>
+          <t>50,58%</t>
         </is>
       </c>
     </row>
@@ -6086,12 +6086,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>2786</t>
+          <t>2350</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>11394</t>
+          <t>10709</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -6101,12 +6101,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>3,02%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -6121,12 +6121,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>3828</t>
+          <t>3618</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>13210</t>
+          <t>12805</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6136,12 +6136,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>3,62%</t>
+          <t>3,51%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6156,12 +6156,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>8117</t>
+          <t>8054</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>20205</t>
+          <t>20029</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6171,12 +6171,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>2,78%</t>
         </is>
       </c>
     </row>
@@ -6199,12 +6199,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>157786</t>
+          <t>157991</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>189593</t>
+          <t>187322</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6214,12 +6214,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>44,51%</t>
+          <t>44,57%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>53,48%</t>
+          <t>52,84%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6234,12 +6234,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>156224</t>
+          <t>156736</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>189022</t>
+          <t>190107</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6249,12 +6249,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>42,8%</t>
+          <t>42,94%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>51,79%</t>
+          <t>52,09%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6269,12 +6269,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>323262</t>
+          <t>324611</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>367097</t>
+          <t>368551</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6284,12 +6284,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>44,93%</t>
+          <t>45,12%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>51,02%</t>
+          <t>51,22%</t>
         </is>
       </c>
     </row>
@@ -6312,12 +6312,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>4174</t>
+          <t>4064</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>13341</t>
+          <t>12918</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6327,12 +6327,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>3,64%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6347,12 +6347,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>10858</t>
+          <t>10205</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>23754</t>
+          <t>23372</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6362,12 +6362,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>6,51%</t>
+          <t>6,4%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6382,12 +6382,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>16754</t>
+          <t>16594</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>32528</t>
+          <t>32385</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6397,12 +6397,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>4,52%</t>
+          <t>4,5%</t>
         </is>
       </c>
     </row>
@@ -6425,12 +6425,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>150768</t>
+          <t>152541</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>183591</t>
+          <t>182451</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -6440,12 +6440,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>42,53%</t>
+          <t>43,03%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>51,79%</t>
+          <t>51,47%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -6460,12 +6460,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>152713</t>
+          <t>152466</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>184650</t>
+          <t>185693</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -6475,12 +6475,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>41,84%</t>
+          <t>41,77%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>50,59%</t>
+          <t>50,88%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -6495,12 +6495,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>315884</t>
+          <t>314041</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>359062</t>
+          <t>357370</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -6510,12 +6510,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>43,9%</t>
+          <t>43,65%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>49,9%</t>
+          <t>49,67%</t>
         </is>
       </c>
     </row>
@@ -6892,7 +6892,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>2989</t>
+          <t>4044</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6907,7 +6907,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,38%</t>
+          <t>5,93%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6927,7 +6927,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>5372</t>
+          <t>5344</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6942,7 +6942,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>7,09%</t>
+          <t>7,05%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6957,12 +6957,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>602</t>
+          <t>600</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>5875</t>
+          <t>6481</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6977,7 +6977,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>4,5%</t>
         </is>
       </c>
     </row>
@@ -7000,12 +7000,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>30490</t>
+          <t>30078</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>44123</t>
+          <t>43947</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7015,12 +7015,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>44,69%</t>
+          <t>44,09%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>64,67%</t>
+          <t>64,41%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7035,12 +7035,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>31254</t>
+          <t>31634</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>45815</t>
+          <t>46278</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7050,12 +7050,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>41,22%</t>
+          <t>41,72%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>60,42%</t>
+          <t>61,04%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7070,12 +7070,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>65021</t>
+          <t>64668</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>85986</t>
+          <t>85491</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7085,12 +7085,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>45,14%</t>
+          <t>44,89%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>59,69%</t>
+          <t>59,35%</t>
         </is>
       </c>
     </row>
@@ -7113,12 +7113,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>613</t>
+          <t>629</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>6300</t>
+          <t>7092</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -7128,12 +7128,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>9,23%</t>
+          <t>10,39%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -7153,7 +7153,7 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>3628</t>
+          <t>3677</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -7168,7 +7168,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>4,78%</t>
+          <t>4,85%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -7188,7 +7188,7 @@
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>7746</t>
+          <t>7059</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -7203,7 +7203,7 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>5,38%</t>
+          <t>4,9%</t>
         </is>
       </c>
     </row>
@@ -7226,12 +7226,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>21301</t>
+          <t>21610</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>34831</t>
+          <t>35547</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7241,12 +7241,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>31,22%</t>
+          <t>31,67%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>51,05%</t>
+          <t>52,1%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7261,12 +7261,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>27517</t>
+          <t>27331</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>42353</t>
+          <t>42093</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7276,12 +7276,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>36,29%</t>
+          <t>36,05%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>55,86%</t>
+          <t>55,52%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7296,12 +7296,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>52973</t>
+          <t>53464</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>73457</t>
+          <t>74661</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7311,12 +7311,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>36,78%</t>
+          <t>37,12%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>51,0%</t>
+          <t>51,83%</t>
         </is>
       </c>
     </row>
@@ -7456,12 +7456,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1239</t>
+          <t>1251</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>7291</t>
+          <t>7877</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -7471,12 +7471,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>6,91%</t>
+          <t>7,46%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -7491,12 +7491,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1629</t>
+          <t>2021</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>9395</t>
+          <t>9166</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -7506,12 +7506,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>8,89%</t>
+          <t>8,67%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -7526,12 +7526,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>4357</t>
+          <t>4192</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>13724</t>
+          <t>13429</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -7541,12 +7541,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>1,98%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>6,5%</t>
+          <t>6,36%</t>
         </is>
       </c>
     </row>
@@ -7569,12 +7569,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>49207</t>
+          <t>50393</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>66586</t>
+          <t>66427</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7584,12 +7584,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>46,63%</t>
+          <t>47,75%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>63,1%</t>
+          <t>62,94%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7604,12 +7604,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>48035</t>
+          <t>47930</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>64518</t>
+          <t>65148</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7619,12 +7619,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>45,44%</t>
+          <t>45,34%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>61,03%</t>
+          <t>61,62%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7639,12 +7639,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>102940</t>
+          <t>103555</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>126542</t>
+          <t>126586</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7654,12 +7654,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>48,73%</t>
+          <t>49,02%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>59,9%</t>
+          <t>59,92%</t>
         </is>
       </c>
     </row>
@@ -7682,12 +7682,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1209</t>
+          <t>1202</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>7224</t>
+          <t>7249</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7697,12 +7697,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>6,85%</t>
+          <t>6,87%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7722,7 +7722,7 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>4497</t>
+          <t>4504</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7737,7 +7737,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>4,25%</t>
+          <t>4,26%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7752,12 +7752,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>2306</t>
+          <t>1905</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>9029</t>
+          <t>9146</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7767,12 +7767,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>4,27%</t>
+          <t>4,33%</t>
         </is>
       </c>
     </row>
@@ -7795,12 +7795,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>31720</t>
+          <t>32171</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>48635</t>
+          <t>48405</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -7810,12 +7810,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>30,06%</t>
+          <t>30,48%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>46,09%</t>
+          <t>45,87%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -7830,12 +7830,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>35815</t>
+          <t>34815</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>51370</t>
+          <t>52216</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7845,12 +7845,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>33,88%</t>
+          <t>32,93%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>48,59%</t>
+          <t>49,39%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -7865,12 +7865,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>72170</t>
+          <t>72260</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>94877</t>
+          <t>95629</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7880,12 +7880,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>34,16%</t>
+          <t>34,21%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>44,91%</t>
+          <t>45,27%</t>
         </is>
       </c>
     </row>
@@ -8030,7 +8030,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>4757</t>
+          <t>4176</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8045,7 +8045,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>6,34%</t>
+          <t>5,57%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8065,7 +8065,7 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3208</t>
+          <t>3739</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8080,7 +8080,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>4,27%</t>
+          <t>4,97%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8095,12 +8095,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>643</t>
+          <t>649</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>5544</t>
+          <t>5487</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8115,7 +8115,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>3,65%</t>
         </is>
       </c>
     </row>
@@ -8138,12 +8138,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>38944</t>
+          <t>38695</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>52249</t>
+          <t>52148</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -8153,12 +8153,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>51,91%</t>
+          <t>51,58%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>69,65%</t>
+          <t>69,51%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -8173,12 +8173,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>38634</t>
+          <t>38892</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>52171</t>
+          <t>53221</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -8188,12 +8188,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>51,38%</t>
+          <t>51,72%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>69,38%</t>
+          <t>70,78%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -8208,12 +8208,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>81679</t>
+          <t>82539</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>100750</t>
+          <t>101140</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -8223,12 +8223,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>54,38%</t>
+          <t>54,95%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>67,07%</t>
+          <t>67,33%</t>
         </is>
       </c>
     </row>
@@ -8251,12 +8251,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>699</t>
+          <t>686</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>6015</t>
+          <t>6303</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8266,12 +8266,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>8,02%</t>
+          <t>8,4%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8286,12 +8286,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>585</t>
+          <t>583</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>5338</t>
+          <t>5746</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8306,7 +8306,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>7,1%</t>
+          <t>7,64%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8321,12 +8321,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>2118</t>
+          <t>1955</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>9297</t>
+          <t>9191</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8336,12 +8336,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>6,19%</t>
+          <t>6,12%</t>
         </is>
       </c>
     </row>
@@ -8364,12 +8364,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>18949</t>
+          <t>18597</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>31351</t>
+          <t>31512</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8379,12 +8379,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>25,26%</t>
+          <t>24,79%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>41,79%</t>
+          <t>42,01%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8399,12 +8399,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>20155</t>
+          <t>19030</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>33792</t>
+          <t>33043</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8414,12 +8414,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>26,8%</t>
+          <t>25,31%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>44,94%</t>
+          <t>43,94%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8434,12 +8434,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>42657</t>
+          <t>42861</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>62053</t>
+          <t>60823</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8449,12 +8449,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>28,4%</t>
+          <t>28,53%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>41,31%</t>
+          <t>40,49%</t>
         </is>
       </c>
     </row>
@@ -8594,12 +8594,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>683</t>
+          <t>675</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>6225</t>
+          <t>5834</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8609,12 +8609,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>5,64%</t>
+          <t>5,28%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8634,7 +8634,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>2985</t>
+          <t>2967</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8649,7 +8649,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>2,78%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8664,12 +8664,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>694</t>
+          <t>688</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>6280</t>
+          <t>6159</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8684,7 +8684,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>2,84%</t>
         </is>
       </c>
     </row>
@@ -8707,12 +8707,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>60200</t>
+          <t>60357</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>77822</t>
+          <t>77796</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -8722,12 +8722,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>54,52%</t>
+          <t>54,66%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>70,47%</t>
+          <t>70,45%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8742,12 +8742,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>55597</t>
+          <t>55732</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>72483</t>
+          <t>72860</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -8757,12 +8757,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>52,15%</t>
+          <t>52,28%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>67,99%</t>
+          <t>68,34%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8777,12 +8777,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>121444</t>
+          <t>121928</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>145552</t>
+          <t>145527</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -8792,12 +8792,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>55,96%</t>
+          <t>56,18%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>67,06%</t>
+          <t>67,05%</t>
         </is>
       </c>
     </row>
@@ -8820,12 +8820,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>3486</t>
+          <t>3991</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>13142</t>
+          <t>12792</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -8835,12 +8835,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>3,61%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>11,9%</t>
+          <t>11,58%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -8855,12 +8855,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>693</t>
+          <t>675</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>6952</t>
+          <t>6306</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -8870,12 +8870,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>6,52%</t>
+          <t>5,92%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -8890,12 +8890,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>5791</t>
+          <t>5795</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>16452</t>
+          <t>16447</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -8933,12 +8933,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>23814</t>
+          <t>23595</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>40633</t>
+          <t>39770</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8948,12 +8948,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>21,57%</t>
+          <t>21,37%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>36,8%</t>
+          <t>36,02%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8968,12 +8968,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>31096</t>
+          <t>31033</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>47634</t>
+          <t>48061</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8983,12 +8983,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>29,17%</t>
+          <t>29,11%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>44,68%</t>
+          <t>45,08%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9003,12 +9003,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>58475</t>
+          <t>59656</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>82646</t>
+          <t>83393</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9018,12 +9018,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>26,94%</t>
+          <t>27,49%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>38,08%</t>
+          <t>38,42%</t>
         </is>
       </c>
     </row>
@@ -9163,12 +9163,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>3982</t>
+          <t>4279</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>12759</t>
+          <t>12915</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -9178,12 +9178,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -9198,12 +9198,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>3528</t>
+          <t>3674</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>12967</t>
+          <t>12868</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -9213,12 +9213,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>3,54%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -9233,12 +9233,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>10026</t>
+          <t>9255</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>22206</t>
+          <t>22065</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -9248,12 +9248,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>3,05%</t>
         </is>
       </c>
     </row>
@@ -9276,12 +9276,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>195975</t>
+          <t>194832</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>225812</t>
+          <t>225331</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9291,12 +9291,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>54,56%</t>
+          <t>54,24%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>62,87%</t>
+          <t>62,73%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9311,12 +9311,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>190170</t>
+          <t>190288</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>221690</t>
+          <t>222124</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9326,12 +9326,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>52,34%</t>
+          <t>52,37%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>61,01%</t>
+          <t>61,13%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9346,12 +9346,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>392829</t>
+          <t>395099</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>437516</t>
+          <t>437752</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9361,12 +9361,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>54,37%</t>
+          <t>54,68%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>60,55%</t>
+          <t>60,58%</t>
         </is>
       </c>
     </row>
@@ -9389,12 +9389,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>10255</t>
+          <t>10601</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>23845</t>
+          <t>23903</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9404,12 +9404,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>2,95%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>6,64%</t>
+          <t>6,65%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9424,12 +9424,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3158</t>
+          <t>3714</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>12139</t>
+          <t>12450</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9439,12 +9439,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,43%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9459,12 +9459,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>16485</t>
+          <t>16426</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>30641</t>
+          <t>31964</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9474,12 +9474,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>4,24%</t>
+          <t>4,42%</t>
         </is>
       </c>
     </row>
@@ -9502,12 +9502,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>109721</t>
+          <t>111049</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>139371</t>
+          <t>141241</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -9517,12 +9517,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>30,55%</t>
+          <t>30,92%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>38,8%</t>
+          <t>39,32%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -9537,12 +9537,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>128649</t>
+          <t>127986</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>159801</t>
+          <t>159245</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -9552,12 +9552,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>35,41%</t>
+          <t>35,22%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>43,98%</t>
+          <t>43,83%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -9572,12 +9572,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>247456</t>
+          <t>246997</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>290473</t>
+          <t>288664</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -9587,12 +9587,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>34,25%</t>
+          <t>34,18%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>40,2%</t>
+          <t>39,95%</t>
         </is>
       </c>
     </row>
@@ -10077,12 +10077,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>46926</t>
+          <t>46779</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>58070</t>
+          <t>58062</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -10092,12 +10092,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>67,26%</t>
+          <t>67,05%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>83,24%</t>
+          <t>83,22%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -10112,12 +10112,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>60203</t>
+          <t>61269</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>75871</t>
+          <t>76973</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -10127,12 +10127,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>70,62%</t>
+          <t>71,87%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>89,0%</t>
+          <t>90,29%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -10147,12 +10147,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>111320</t>
+          <t>112146</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>131724</t>
+          <t>131202</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -10162,12 +10162,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>71,81%</t>
+          <t>72,35%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>84,98%</t>
+          <t>84,64%</t>
         </is>
       </c>
     </row>
@@ -10195,7 +10195,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>4226</t>
+          <t>3708</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -10210,7 +10210,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>6,06%</t>
+          <t>5,32%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -10265,7 +10265,7 @@
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>4424</t>
+          <t>4457</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -10280,7 +10280,7 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>2,88%</t>
         </is>
       </c>
     </row>
@@ -10303,12 +10303,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>10593</t>
+          <t>10501</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>21790</t>
+          <t>21573</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -10318,12 +10318,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>15,18%</t>
+          <t>15,05%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>31,23%</t>
+          <t>30,92%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -10338,12 +10338,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>9378</t>
+          <t>8276</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>25046</t>
+          <t>23980</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -10353,12 +10353,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>11,0%</t>
+          <t>9,71%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>29,38%</t>
+          <t>28,13%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -10373,12 +10373,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>21740</t>
+          <t>22699</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>41598</t>
+          <t>41166</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -10388,12 +10388,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>14,02%</t>
+          <t>14,64%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>26,83%</t>
+          <t>26,56%</t>
         </is>
       </c>
     </row>
@@ -10533,12 +10533,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>366</t>
+          <t>369</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>5890</t>
+          <t>6358</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -10553,7 +10553,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>5,18%</t>
+          <t>5,59%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -10603,12 +10603,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>368</t>
+          <t>372</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>6107</t>
+          <t>5942</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -10623,7 +10623,7 @@
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,11%</t>
         </is>
       </c>
     </row>
@@ -10646,12 +10646,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>85760</t>
+          <t>85610</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>99417</t>
+          <t>99586</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -10661,12 +10661,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>75,4%</t>
+          <t>75,27%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>87,41%</t>
+          <t>87,56%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -10681,12 +10681,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>122552</t>
+          <t>122564</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>142094</t>
+          <t>142283</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -10696,12 +10696,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>73,22%</t>
+          <t>73,23%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>84,9%</t>
+          <t>85,01%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -10716,12 +10716,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>213258</t>
+          <t>213405</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>237164</t>
+          <t>236711</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -10731,12 +10731,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>75,86%</t>
+          <t>75,92%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>84,37%</t>
+          <t>84,21%</t>
         </is>
       </c>
     </row>
@@ -10764,7 +10764,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>3933</t>
+          <t>2859</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -10779,7 +10779,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>2,51%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -10799,7 +10799,7 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>4278</t>
+          <t>4191</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -10814,7 +10814,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -10834,7 +10834,7 @@
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>5005</t>
+          <t>5391</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -10849,7 +10849,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,92%</t>
         </is>
       </c>
     </row>
@@ -10872,12 +10872,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>12104</t>
+          <t>12048</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>24753</t>
+          <t>24748</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -10887,7 +10887,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>10,64%</t>
+          <t>10,59%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -10907,12 +10907,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>24379</t>
+          <t>24063</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>44388</t>
+          <t>43851</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -10922,12 +10922,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>14,57%</t>
+          <t>14,38%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>26,52%</t>
+          <t>26,2%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -10942,12 +10942,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>40682</t>
+          <t>41291</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>63995</t>
+          <t>64167</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -10957,12 +10957,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>14,47%</t>
+          <t>14,69%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>22,77%</t>
+          <t>22,83%</t>
         </is>
       </c>
     </row>
@@ -11107,7 +11107,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>886</t>
+          <t>852</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -11122,7 +11122,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -11177,7 +11177,7 @@
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>953</t>
+          <t>974</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -11192,7 +11192,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,43%</t>
         </is>
       </c>
     </row>
@@ -11215,12 +11215,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>68500</t>
+          <t>68350</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>86375</t>
+          <t>86534</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -11230,12 +11230,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>63,56%</t>
+          <t>63,42%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>80,14%</t>
+          <t>80,29%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -11250,12 +11250,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>76728</t>
+          <t>78374</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>98469</t>
+          <t>98726</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -11265,12 +11265,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>63,81%</t>
+          <t>65,18%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>81,89%</t>
+          <t>82,1%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -11285,12 +11285,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>153253</t>
+          <t>152424</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>180947</t>
+          <t>180269</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -11300,12 +11300,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>67,21%</t>
+          <t>66,84%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>79,35%</t>
+          <t>79,06%</t>
         </is>
       </c>
     </row>
@@ -11328,12 +11328,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>162</t>
+          <t>304</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>3760</t>
+          <t>4485</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -11343,12 +11343,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,15%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>4,16%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -11363,12 +11363,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1758</t>
+          <t>1827</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>10583</t>
+          <t>10580</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -11378,7 +11378,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -11398,12 +11398,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>2488</t>
+          <t>2665</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>11322</t>
+          <t>11972</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -11413,12 +11413,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,97%</t>
+          <t>5,25%</t>
         </is>
       </c>
     </row>
@@ -11441,12 +11441,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>19464</t>
+          <t>19821</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>37335</t>
+          <t>37568</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -11456,12 +11456,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>18,06%</t>
+          <t>18,39%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>34,64%</t>
+          <t>34,86%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -11476,12 +11476,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>17597</t>
+          <t>17357</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>39052</t>
+          <t>37201</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -11491,12 +11491,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>14,63%</t>
+          <t>14,43%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>32,48%</t>
+          <t>30,94%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -11511,12 +11511,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>41670</t>
+          <t>41657</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>69119</t>
+          <t>67923</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -11531,7 +11531,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>30,31%</t>
+          <t>29,79%</t>
         </is>
       </c>
     </row>
@@ -11676,7 +11676,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>801</t>
+          <t>856</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -11691,7 +11691,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -11711,7 +11711,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>3458</t>
+          <t>5105</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -11726,7 +11726,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>4,6%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -11746,7 +11746,7 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>4850</t>
+          <t>5283</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -11761,7 +11761,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,49%</t>
         </is>
       </c>
     </row>
@@ -11784,12 +11784,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>81335</t>
+          <t>81420</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>92764</t>
+          <t>92645</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -11799,12 +11799,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>80,39%</t>
+          <t>80,47%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>91,68%</t>
+          <t>91,57%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -11819,12 +11819,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>83950</t>
+          <t>84352</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>99046</t>
+          <t>98710</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -11834,12 +11834,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>75,63%</t>
+          <t>75,99%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>89,23%</t>
+          <t>88,92%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -11854,12 +11854,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>170271</t>
+          <t>169991</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>188566</t>
+          <t>188555</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -11869,12 +11869,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>80,25%</t>
+          <t>80,11%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>88,87%</t>
+          <t>88,86%</t>
         </is>
       </c>
     </row>
@@ -11902,7 +11902,7 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>4840</t>
+          <t>5162</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -11917,7 +11917,7 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>4,78%</t>
+          <t>5,1%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -11937,7 +11937,7 @@
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>3876</t>
+          <t>4356</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -11952,7 +11952,7 @@
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>3,92%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -11967,12 +11967,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>643</t>
+          <t>654</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>6201</t>
+          <t>6146</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -11982,12 +11982,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>2,9%</t>
         </is>
       </c>
     </row>
@@ -12010,12 +12010,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>7222</t>
+          <t>7161</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>18420</t>
+          <t>17940</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -12025,12 +12025,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>7,14%</t>
+          <t>7,08%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>18,21%</t>
+          <t>17,73%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -12045,12 +12045,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>10891</t>
+          <t>11048</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>25571</t>
+          <t>25235</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -12060,12 +12060,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>9,81%</t>
+          <t>9,95%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>23,04%</t>
+          <t>22,73%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -12080,12 +12080,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>20660</t>
+          <t>20886</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>38625</t>
+          <t>38588</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -12095,12 +12095,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>9,74%</t>
+          <t>9,84%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>18,2%</t>
+          <t>18,19%</t>
         </is>
       </c>
     </row>
@@ -12240,12 +12240,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>663</t>
+          <t>696</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>6340</t>
+          <t>6338</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -12255,39 +12255,39 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
+          <t>0,18%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>1,61%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>846</t>
+        </is>
+      </c>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>5060</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr">
+        <is>
           <t>0,17%</t>
         </is>
       </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>1,62%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>846</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>4561</t>
-        </is>
-      </c>
-      <c r="N24" s="2" t="inlineStr">
-        <is>
-          <t>0,17%</t>
-        </is>
-      </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
@@ -12295,7 +12295,7 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -12310,12 +12310,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1034</t>
+          <t>905</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>7075</t>
+          <t>6939</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -12325,12 +12325,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>0,12%</t>
+          <t>0,1%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,79%</t>
         </is>
       </c>
     </row>
@@ -12353,12 +12353,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>297619</t>
+          <t>297664</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>325163</t>
+          <t>325569</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -12368,12 +12368,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>75,83%</t>
+          <t>75,85%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>82,85%</t>
+          <t>82,96%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -12388,12 +12388,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>363788</t>
+          <t>363011</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>400066</t>
+          <t>401364</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -12403,12 +12403,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>75,18%</t>
+          <t>75,02%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>82,68%</t>
+          <t>82,95%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -12423,12 +12423,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>675377</t>
+          <t>675793</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>719595</t>
+          <t>719494</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -12438,12 +12438,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>77,07%</t>
+          <t>77,12%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>82,11%</t>
+          <t>82,1%</t>
         </is>
       </c>
     </row>
@@ -12466,12 +12466,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1980</t>
+          <t>1895</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>8419</t>
+          <t>8345</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -12481,12 +12481,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,13%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -12501,12 +12501,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>2624</t>
+          <t>2986</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>12076</t>
+          <t>12510</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -12516,12 +12516,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,59%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -12536,12 +12536,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>5945</t>
+          <t>6025</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>16813</t>
+          <t>17430</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -12551,12 +12551,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>1,99%</t>
         </is>
       </c>
     </row>
@@ -12579,12 +12579,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>60598</t>
+          <t>60905</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>88174</t>
+          <t>88060</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -12594,12 +12594,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>15,44%</t>
+          <t>15,52%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>22,47%</t>
+          <t>22,44%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -12614,12 +12614,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>77251</t>
+          <t>75990</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>112774</t>
+          <t>111955</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -12629,12 +12629,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>15,96%</t>
+          <t>15,7%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>23,31%</t>
+          <t>23,14%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -12649,12 +12649,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>143848</t>
+          <t>142608</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>187968</t>
+          <t>186106</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -12664,12 +12664,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>16,41%</t>
+          <t>16,27%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>21,45%</t>
+          <t>21,24%</t>
         </is>
       </c>
     </row>
